--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-19T17:20:25+00:00</t>
+    <t>2026-07-21T08:40:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:40:48+00:00</t>
+    <t>2026-07-21T15:50:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T15:50:20+00:00</t>
+    <t>2026-07-21T16:28:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:28:50+00:00</t>
+    <t>2026-07-21T16:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T16:53:48+00:00</t>
+    <t>2026-07-22T08:07:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T08:07:11+00:00</t>
+    <t>2026-07-22T10:39:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T10:39:39+00:00</t>
+    <t>2026-07-22T17:16:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T17:16:50+00:00</t>
+    <t>2026-07-23T08:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T08:53:51+00:00</t>
+    <t>2026-07-23T14:32:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-snr.xlsx
+++ b/spec-tech/ig/StructureDefinition-snr.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,7 +253,7 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">string
+    <t xml:space="preserve">Extension {elementdefinition-identifier|5.3.0}
 </t>
   </si>
 </sst>
@@ -569,7 +569,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="7.6796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="37.140625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
